--- a/frontend/public/templates/inventaire lots pharmaceutiques2024.xlsx
+++ b/frontend/public/templates/inventaire lots pharmaceutiques2024.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Direction Régionale </t>
   </si>
   <si>
-    <t>Gasii Touil</t>
+    <t>Gassi Touil</t>
   </si>
   <si>
     <t>Division Personnel</t>
@@ -1254,9 +1254,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" ns3:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="43.140625" style="1" customWidth="1"/>
@@ -1266,32 +1266,32 @@
     <col min="6" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ns3:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ns3:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ns3:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ns3:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ns3:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.75" ns3:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
         <v>82</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
     </row>
-    <row r="8" spans="1:5" ht="17.25" thickBot="1" ns3:dyDescent="0.35"/>
+    <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="9" customFormat="1" ht="24" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>83</v>
@@ -1319,9 +1319,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A49:D49"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.51181102362204722" top="0.19685039370078741" bottom="0.94488188976377951" header="0.31496062992125984" footer="0.31496062992125984"/>
